--- a/practicas/org_dig_tools/plantillas/solucion.xlsx
+++ b/practicas/org_dig_tools/plantillas/solucion.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupstucom-my.sharepoint.com/personal/llorenc_huguet_365_stucom_com/Documents/Documentos/GitHub/Digi_Eval/org_dig_tools/plantillas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupstucom-my.sharepoint.com/personal/llorenc_huguet_365_stucom_com/Documents/Documentos/GitHub/Digitalizacion/practicas/org_dig_tools/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="79" documentId="8_{09108FAD-DB1D-4446-BBC7-303D3CECCADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C81B60-77EB-416E-B131-3C51AAA614BF}"/>
   <bookViews>
-    <workbookView xWindow="-15615" yWindow="-6135" windowWidth="17625" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOLUTION" sheetId="1" r:id="rId1"/>
